--- a/output/daily_ratings/uk_ratings_2026-06-17.xlsx
+++ b/output/daily_ratings/uk_ratings_2026-06-17.xlsx
@@ -524,11 +524,11 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Your Song (IRE)</t>
+          <t>Victorious (IRE)</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -544,14 +544,16 @@
       <c r="M2" t="n">
         <v>59.19</v>
       </c>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" t="n">
+        <v>109.4</v>
+      </c>
       <c r="O2" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>-28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -580,11 +582,11 @@
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Victorious (IRE)</t>
+          <t>Senorita Bonita (IRE)</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -596,12 +598,14 @@
       <c r="K3" t="n">
         <v>0</v>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>2</v>
+      </c>
       <c r="M3" t="n">
         <v>59.19</v>
       </c>
       <c r="N3" t="n">
-        <v>109.4</v>
+        <v>102.1</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -638,11 +642,11 @@
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Senorita Bonita (IRE)</t>
+          <t>Ruiva (USA)</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -655,13 +659,13 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="M4" t="n">
         <v>59.19</v>
       </c>
       <c r="N4" t="n">
-        <v>102.1</v>
+        <v>100.9</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -698,11 +702,11 @@
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Ruiva (USA)</t>
+          <t>Pershaada (IRE)</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -715,13 +719,13 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>2.03</v>
+        <v>2.53</v>
       </c>
       <c r="M5" t="n">
         <v>59.19</v>
       </c>
       <c r="N5" t="n">
-        <v>100.9</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -758,11 +762,11 @@
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Pershaada (IRE)</t>
+          <t>Crownbreaker (IRE)</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -775,13 +779,13 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>2.53</v>
+        <v>3.28</v>
       </c>
       <c r="M6" t="n">
         <v>59.19</v>
       </c>
       <c r="N6" t="n">
-        <v>96.90000000000001</v>
+        <v>92.7</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -818,11 +822,11 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Crownbreaker (IRE)</t>
+          <t>Alta Regina (IRE)</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -835,13 +839,13 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>3.28</v>
+        <v>3.43</v>
       </c>
       <c r="M7" t="n">
         <v>59.19</v>
       </c>
       <c r="N7" t="n">
-        <v>92.7</v>
+        <v>91</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -878,11 +882,11 @@
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Alta Regina (IRE)</t>
+          <t>Shimmering Sun (IRE)</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -895,13 +899,13 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>3.43</v>
+        <v>3.53</v>
       </c>
       <c r="M8" t="n">
         <v>59.19</v>
       </c>
       <c r="N8" t="n">
-        <v>91</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -938,11 +942,11 @@
         <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Shimmering Sun (IRE)</t>
+          <t>Velozee (IRE)</t>
         </is>
       </c>
       <c r="I9" t="n">
@@ -955,13 +959,13 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>3.53</v>
+        <v>3.56</v>
       </c>
       <c r="M9" t="n">
         <v>59.19</v>
       </c>
       <c r="N9" t="n">
-        <v>90.59999999999999</v>
+        <v>89.5</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -998,11 +1002,11 @@
         <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Velozee (IRE)</t>
+          <t>Armor Supreme (IRE)</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -1015,13 +1019,13 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>3.56</v>
+        <v>3.66</v>
       </c>
       <c r="M10" t="n">
         <v>59.19</v>
       </c>
       <c r="N10" t="n">
-        <v>89.5</v>
+        <v>88.7</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1058,11 +1062,11 @@
         <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Armor Supreme (IRE)</t>
+          <t>Wild Blossom (IRE)</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -1075,13 +1079,13 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>3.66</v>
+        <v>4.16</v>
       </c>
       <c r="M11" t="n">
         <v>59.19</v>
       </c>
       <c r="N11" t="n">
-        <v>88.7</v>
+        <v>86.3</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -1118,11 +1122,11 @@
         <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Wild Blossom (IRE)</t>
+          <t>Miss Lizzy</t>
         </is>
       </c>
       <c r="I12" t="n">
@@ -1135,13 +1139,13 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>4.16</v>
+        <v>4.26</v>
       </c>
       <c r="M12" t="n">
         <v>59.19</v>
       </c>
       <c r="N12" t="n">
-        <v>86.3</v>
+        <v>85.8</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1178,11 +1182,11 @@
         <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Miss Lizzy</t>
+          <t>Drazinda (FR)</t>
         </is>
       </c>
       <c r="I13" t="n">
@@ -1195,13 +1199,13 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>4.26</v>
+        <v>5.26</v>
       </c>
       <c r="M13" t="n">
         <v>59.19</v>
       </c>
       <c r="N13" t="n">
-        <v>85.8</v>
+        <v>81</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -1238,11 +1242,11 @@
         <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Drazinda (FR)</t>
+          <t>Crystal Queen (IRE)</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -1255,13 +1259,13 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>5.26</v>
+        <v>5.36</v>
       </c>
       <c r="M14" t="n">
         <v>59.19</v>
       </c>
       <c r="N14" t="n">
-        <v>81</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -1298,11 +1302,11 @@
         <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Crystal Queen (IRE)</t>
+          <t>Fast Track (IRE)</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -1315,13 +1319,13 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>5.36</v>
+        <v>5.46</v>
       </c>
       <c r="M15" t="n">
         <v>59.19</v>
       </c>
       <c r="N15" t="n">
-        <v>80.09999999999999</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -1358,11 +1362,11 @@
         <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Fast Track (IRE)</t>
+          <t>Big Negotiator</t>
         </is>
       </c>
       <c r="I16" t="n">
@@ -1375,13 +1379,13 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>5.46</v>
+        <v>5.96</v>
       </c>
       <c r="M16" t="n">
         <v>59.19</v>
       </c>
       <c r="N16" t="n">
-        <v>79.59999999999999</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -1418,11 +1422,11 @@
         <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Big Negotiator</t>
+          <t>Kentucky Rain (IRE)</t>
         </is>
       </c>
       <c r="I17" t="n">
@@ -1435,13 +1439,13 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>5.96</v>
+        <v>6.46</v>
       </c>
       <c r="M17" t="n">
         <v>59.19</v>
       </c>
       <c r="N17" t="n">
-        <v>78.59999999999999</v>
+        <v>77.3</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -1478,11 +1482,11 @@
         <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Kentucky Rain (IRE)</t>
+          <t>Princesse Dorange</t>
         </is>
       </c>
       <c r="I18" t="n">
@@ -1495,13 +1499,13 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>6.46</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="M18" t="n">
         <v>59.19</v>
       </c>
       <c r="N18" t="n">
-        <v>77.3</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -1509,7 +1513,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="19">
@@ -1538,11 +1542,11 @@
         <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Princesse Dorange</t>
+          <t>Havana Lightning</t>
         </is>
       </c>
       <c r="I19" t="n">
@@ -1555,7 +1559,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>9.710000000000001</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="M19" t="n">
         <v>59.19</v>
@@ -1569,7 +1573,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>-0.5</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="20">
@@ -1598,11 +1602,11 @@
         <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Havana Lightning</t>
+          <t>More Champagne (USA)</t>
         </is>
       </c>
       <c r="I20" t="n">
@@ -1615,13 +1619,13 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>9.859999999999999</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="M20" t="n">
         <v>59.19</v>
       </c>
       <c r="N20" t="n">
-        <v>67.40000000000001</v>
+        <v>66</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -1629,7 +1633,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1658,11 +1662,11 @@
         <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>More Champagne (USA)</t>
+          <t>Love A Giggle (IRE)</t>
         </is>
       </c>
       <c r="I21" t="n">
@@ -1675,13 +1679,13 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>9.960000000000001</v>
+        <v>10.71</v>
       </c>
       <c r="M21" t="n">
         <v>59.19</v>
       </c>
       <c r="N21" t="n">
-        <v>66</v>
+        <v>60.3</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -1718,11 +1722,11 @@
         <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Love A Giggle (IRE)</t>
+          <t>Magic Effort</t>
         </is>
       </c>
       <c r="I22" t="n">
@@ -1735,13 +1739,13 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>10.71</v>
+        <v>12.96</v>
       </c>
       <c r="M22" t="n">
         <v>59.19</v>
       </c>
       <c r="N22" t="n">
-        <v>60.3</v>
+        <v>56.2</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -1778,11 +1782,11 @@
         <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Magic Effort</t>
+          <t>Envision</t>
         </is>
       </c>
       <c r="I23" t="n">
@@ -1795,13 +1799,13 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>12.96</v>
+        <v>13.46</v>
       </c>
       <c r="M23" t="n">
         <v>59.19</v>
       </c>
       <c r="N23" t="n">
-        <v>56.2</v>
+        <v>54.7</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -1838,11 +1842,11 @@
         <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Envision</t>
+          <t>Lover Girl (IRE)</t>
         </is>
       </c>
       <c r="I24" t="n">
@@ -1855,13 +1859,13 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>13.46</v>
+        <v>14.46</v>
       </c>
       <c r="M24" t="n">
         <v>59.19</v>
       </c>
       <c r="N24" t="n">
-        <v>54.7</v>
+        <v>52.3</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -1898,11 +1902,11 @@
         <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Lover Girl (IRE)</t>
+          <t>Shining Moment (USA)</t>
         </is>
       </c>
       <c r="I25" t="n">
@@ -1912,16 +1916,16 @@
         <v>128</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="L25" t="n">
-        <v>14.46</v>
+        <v>15.46</v>
       </c>
       <c r="M25" t="n">
         <v>59.19</v>
       </c>
       <c r="N25" t="n">
-        <v>52.3</v>
+        <v>44.3</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
@@ -1958,11 +1962,11 @@
         <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Shining Moment (USA)</t>
+          <t>Niewiadoma (IRE)</t>
         </is>
       </c>
       <c r="I26" t="n">
@@ -1972,16 +1976,16 @@
         <v>128</v>
       </c>
       <c r="K26" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>15.46</v>
+        <v>15.96</v>
       </c>
       <c r="M26" t="n">
         <v>59.19</v>
       </c>
       <c r="N26" t="n">
-        <v>44.3</v>
+        <v>42.9</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -2018,11 +2022,11 @@
         <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Niewiadoma (IRE)</t>
+          <t>Celtic Dispute (USA)</t>
         </is>
       </c>
       <c r="I27" t="n">
@@ -2032,16 +2036,16 @@
         <v>128</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="L27" t="n">
-        <v>15.96</v>
+        <v>16.71</v>
       </c>
       <c r="M27" t="n">
         <v>59.19</v>
       </c>
       <c r="N27" t="n">
-        <v>42.9</v>
+        <v>42</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
@@ -2078,11 +2082,11 @@
         <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Celtic Dispute (USA)</t>
+          <t>Bint Archange (IRE)</t>
         </is>
       </c>
       <c r="I28" t="n">
@@ -2092,16 +2096,16 @@
         <v>128</v>
       </c>
       <c r="K28" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>16.71</v>
+        <v>18.46</v>
       </c>
       <c r="M28" t="n">
         <v>59.19</v>
       </c>
       <c r="N28" t="n">
-        <v>42</v>
+        <v>36.1</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -2137,40 +2141,24 @@
       <c r="F29" t="n">
         <v>1</v>
       </c>
-      <c r="G29" t="n">
-        <v>27</v>
-      </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Bint Archange (IRE)</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
-        <v>2</v>
-      </c>
-      <c r="J29" t="n">
-        <v>128</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>18.46</v>
-      </c>
-      <c r="M29" t="n">
-        <v>59.19</v>
-      </c>
-      <c r="N29" t="n">
-        <v>36.1</v>
-      </c>
+          <t>Your Song (IRE)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
+      <c r="P29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2633,7 +2621,7 @@
         <v>84</v>
       </c>
       <c r="L37" t="n">
-        <v>8.68</v>
+        <v>8.680000000000001</v>
       </c>
       <c r="M37" t="n">
         <v>182.07</v>
@@ -4232,34 +4220,36 @@
         <v>2</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Linwood (IRE)</t>
+          <t>Rogue Diplomat (IRE)</t>
         </is>
       </c>
       <c r="I64" t="n">
         <v>4</v>
       </c>
       <c r="J64" t="n">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="K64" t="n">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="n">
         <v>99.23999999999999</v>
       </c>
-      <c r="N64" t="inlineStr"/>
+      <c r="N64" t="n">
+        <v>95.90000000000001</v>
+      </c>
       <c r="O64" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P64" t="n">
-        <v>-29.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -4288,34 +4278,38 @@
         <v>2</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Chibitty (FR)</t>
+          <t>Blue Rc (IRE)</t>
         </is>
       </c>
       <c r="I65" t="n">
         <v>4</v>
       </c>
       <c r="J65" t="n">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="K65" t="n">
-        <v>103</v>
-      </c>
-      <c r="L65" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="L65" t="n">
+        <v>1</v>
+      </c>
       <c r="M65" t="n">
         <v>99.23999999999999</v>
       </c>
-      <c r="N65" t="inlineStr"/>
+      <c r="N65" t="n">
+        <v>95.09999999999999</v>
+      </c>
       <c r="O65" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>-29.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4344,15 +4338,15 @@
         <v>2</v>
       </c>
       <c r="G66" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Rogue Diplomat (IRE)</t>
+          <t>Indalo (IRE)</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J66" t="n">
         <v>126</v>
@@ -4360,12 +4354,14 @@
       <c r="K66" t="n">
         <v>98</v>
       </c>
-      <c r="L66" t="inlineStr"/>
+      <c r="L66" t="n">
+        <v>2.5</v>
+      </c>
       <c r="M66" t="n">
         <v>99.23999999999999</v>
       </c>
       <c r="N66" t="n">
-        <v>95.90000000000001</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
@@ -4373,7 +4369,7 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="67">
@@ -4402,30 +4398,30 @@
         <v>2</v>
       </c>
       <c r="G67" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Blue Rc (IRE)</t>
+          <t>Ebts Guard</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J67" t="n">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="K67" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="L67" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M67" t="n">
         <v>99.23999999999999</v>
       </c>
       <c r="N67" t="n">
-        <v>95.09999999999999</v>
+        <v>93.5</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
@@ -4433,7 +4429,7 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4462,30 +4458,30 @@
         <v>2</v>
       </c>
       <c r="G68" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Indalo (IRE)</t>
+          <t>Cerulean Bay (IRE)</t>
         </is>
       </c>
       <c r="I68" t="n">
         <v>5</v>
       </c>
       <c r="J68" t="n">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="K68" t="n">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="L68" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="M68" t="n">
         <v>99.23999999999999</v>
       </c>
       <c r="N68" t="n">
-        <v>89.40000000000001</v>
+        <v>92.3</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
@@ -4493,7 +4489,7 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4522,30 +4518,30 @@
         <v>2</v>
       </c>
       <c r="G69" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Ebts Guard</t>
+          <t>Erzindjan (IRE)</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J69" t="n">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="K69" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="L69" t="n">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="M69" t="n">
         <v>99.23999999999999</v>
       </c>
       <c r="N69" t="n">
-        <v>93.5</v>
+        <v>88.7</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
@@ -4553,7 +4549,7 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="70">
@@ -4582,30 +4578,30 @@
         <v>2</v>
       </c>
       <c r="G70" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Cerulean Bay (IRE)</t>
+          <t>Scoville</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J70" t="n">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="K70" t="n">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="L70" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="M70" t="n">
         <v>99.23999999999999</v>
       </c>
       <c r="N70" t="n">
-        <v>92.3</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
@@ -4613,7 +4609,7 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="71">
@@ -4642,30 +4638,30 @@
         <v>2</v>
       </c>
       <c r="G71" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Erzindjan (IRE)</t>
+          <t>Ozat (FR)</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J71" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="K71" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L71" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="M71" t="n">
         <v>99.23999999999999</v>
       </c>
       <c r="N71" t="n">
-        <v>88.7</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
@@ -4673,7 +4669,7 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>-3</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="72">
@@ -4702,30 +4698,30 @@
         <v>2</v>
       </c>
       <c r="G72" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Scoville</t>
+          <t>Classic</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J72" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K72" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L72" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="M72" t="n">
         <v>99.23999999999999</v>
       </c>
       <c r="N72" t="n">
-        <v>88.40000000000001</v>
+        <v>88</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
@@ -4733,7 +4729,7 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>-3</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="73">
@@ -4762,30 +4758,30 @@
         <v>2</v>
       </c>
       <c r="G73" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Ozat (FR)</t>
+          <t>Checkandchallenge</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J73" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="K73" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="L73" t="n">
-        <v>3.75</v>
+        <v>4.05</v>
       </c>
       <c r="M73" t="n">
         <v>99.23999999999999</v>
       </c>
       <c r="N73" t="n">
-        <v>88.90000000000001</v>
+        <v>88</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
@@ -4793,7 +4789,7 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0.5</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="74">
@@ -4822,30 +4818,30 @@
         <v>2</v>
       </c>
       <c r="G74" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Classic</t>
+          <t>Fifth Column (IRE)</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J74" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="K74" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="L74" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="M74" t="n">
         <v>99.23999999999999</v>
       </c>
       <c r="N74" t="n">
-        <v>88</v>
+        <v>87.7</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
@@ -4882,15 +4878,15 @@
         <v>2</v>
       </c>
       <c r="G75" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Checkandchallenge</t>
+          <t>Jagged Edge (IRE)</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J75" t="n">
         <v>130</v>
@@ -4899,13 +4895,13 @@
         <v>102</v>
       </c>
       <c r="L75" t="n">
-        <v>4.05</v>
+        <v>4.349999999999999</v>
       </c>
       <c r="M75" t="n">
         <v>99.23999999999999</v>
       </c>
       <c r="N75" t="n">
-        <v>88</v>
+        <v>87.8</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
@@ -4913,7 +4909,7 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>-1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -4942,11 +4938,11 @@
         <v>2</v>
       </c>
       <c r="G76" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Fifth Column (IRE)</t>
+          <t>La Botte</t>
         </is>
       </c>
       <c r="I76" t="n">
@@ -4959,7 +4955,7 @@
         <v>102</v>
       </c>
       <c r="L76" t="n">
-        <v>4.2</v>
+        <v>4.45</v>
       </c>
       <c r="M76" t="n">
         <v>99.23999999999999</v>
@@ -4973,7 +4969,7 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>-3.5</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="77">
@@ -5002,30 +4998,30 @@
         <v>2</v>
       </c>
       <c r="G77" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Jagged Edge (IRE)</t>
+          <t>Swing Vote</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J77" t="n">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="K77" t="n">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="L77" t="n">
-        <v>4.35</v>
+        <v>4.6</v>
       </c>
       <c r="M77" t="n">
         <v>99.23999999999999</v>
       </c>
       <c r="N77" t="n">
-        <v>87.8</v>
+        <v>85.8</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
@@ -5033,7 +5029,7 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="78">
@@ -5062,30 +5058,30 @@
         <v>2</v>
       </c>
       <c r="G78" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>La Botte</t>
+          <t>Thunder Run (IRE)</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J78" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K78" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L78" t="n">
-        <v>4.45</v>
+        <v>4.63</v>
       </c>
       <c r="M78" t="n">
         <v>99.23999999999999</v>
       </c>
       <c r="N78" t="n">
-        <v>87.7</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
@@ -5093,7 +5089,7 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>-1.5</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="79">
@@ -5122,30 +5118,30 @@
         <v>2</v>
       </c>
       <c r="G79" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Swing Vote</t>
+          <t>Shout (IRE)</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J79" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="K79" t="n">
         <v>99</v>
       </c>
       <c r="L79" t="n">
-        <v>4.6</v>
+        <v>5.38</v>
       </c>
       <c r="M79" t="n">
         <v>99.23999999999999</v>
       </c>
       <c r="N79" t="n">
-        <v>85.8</v>
+        <v>79.2</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
@@ -5153,7 +5149,7 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="80">
@@ -5182,30 +5178,30 @@
         <v>2</v>
       </c>
       <c r="G80" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Thunder Run (IRE)</t>
+          <t>Holloway Boy</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J80" t="n">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="K80" t="n">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="L80" t="n">
-        <v>4.63</v>
+        <v>6.63</v>
       </c>
       <c r="M80" t="n">
         <v>99.23999999999999</v>
       </c>
       <c r="N80" t="n">
-        <v>88.90000000000001</v>
+        <v>86.3</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
@@ -5213,7 +5209,7 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>7.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
@@ -5242,30 +5238,30 @@
         <v>2</v>
       </c>
       <c r="G81" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Shout (IRE)</t>
+          <t>Godwinson</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J81" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="K81" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L81" t="n">
-        <v>5.38</v>
+        <v>6.73</v>
       </c>
       <c r="M81" t="n">
         <v>99.23999999999999</v>
       </c>
       <c r="N81" t="n">
-        <v>82.2</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
@@ -5273,7 +5269,7 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="82">
@@ -5302,30 +5298,30 @@
         <v>2</v>
       </c>
       <c r="G82" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Holloway Boy</t>
+          <t>Witch Hunter (FR)</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J82" t="n">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="K82" t="n">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="L82" t="n">
-        <v>6.63</v>
+        <v>6.829999999999999</v>
       </c>
       <c r="M82" t="n">
         <v>99.23999999999999</v>
       </c>
       <c r="N82" t="n">
-        <v>89.59999999999999</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="O82" t="inlineStr">
         <is>
@@ -5333,7 +5329,7 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>12</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="83">
@@ -5362,30 +5358,30 @@
         <v>2</v>
       </c>
       <c r="G83" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Godwinson</t>
+          <t>Archivist</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J83" t="n">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="K83" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="L83" t="n">
-        <v>6.73</v>
+        <v>6.98</v>
       </c>
       <c r="M83" t="n">
         <v>99.23999999999999</v>
       </c>
       <c r="N83" t="n">
-        <v>79.59999999999999</v>
+        <v>84.3</v>
       </c>
       <c r="O83" t="inlineStr">
         <is>
@@ -5393,7 +5389,7 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>-3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
@@ -5422,30 +5418,30 @@
         <v>2</v>
       </c>
       <c r="G84" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Witch Hunter (FR)</t>
+          <t>No Retreat (IRE)</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J84" t="n">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="K84" t="n">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="L84" t="n">
-        <v>6.83</v>
+        <v>7.079999999999999</v>
       </c>
       <c r="M84" t="n">
         <v>99.23999999999999</v>
       </c>
       <c r="N84" t="n">
-        <v>77.90000000000001</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="O84" t="inlineStr">
         <is>
@@ -5453,7 +5449,7 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>-3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="85">
@@ -5482,30 +5478,30 @@
         <v>2</v>
       </c>
       <c r="G85" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Archivist</t>
+          <t>Henlein (AUS)</t>
         </is>
       </c>
       <c r="I85" t="n">
         <v>4</v>
       </c>
       <c r="J85" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="K85" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L85" t="n">
-        <v>6.98</v>
+        <v>7.229999999999999</v>
       </c>
       <c r="M85" t="n">
         <v>99.23999999999999</v>
       </c>
       <c r="N85" t="n">
-        <v>84.3</v>
+        <v>83.5</v>
       </c>
       <c r="O85" t="inlineStr">
         <is>
@@ -5513,7 +5509,7 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="86">
@@ -5542,30 +5538,30 @@
         <v>2</v>
       </c>
       <c r="G86" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>No Retreat (IRE)</t>
+          <t>Mister Winston</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J86" t="n">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="K86" t="n">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="L86" t="n">
-        <v>7.08</v>
+        <v>11.98</v>
       </c>
       <c r="M86" t="n">
         <v>99.23999999999999</v>
       </c>
       <c r="N86" t="n">
-        <v>85.40000000000001</v>
+        <v>68</v>
       </c>
       <c r="O86" t="inlineStr">
         <is>
@@ -5573,7 +5569,7 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -5602,30 +5598,30 @@
         <v>2</v>
       </c>
       <c r="G87" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Henlein (AUS)</t>
+          <t>Skukuza</t>
         </is>
       </c>
       <c r="I87" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J87" t="n">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="K87" t="n">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="L87" t="n">
-        <v>7.23</v>
+        <v>16.73</v>
       </c>
       <c r="M87" t="n">
         <v>99.23999999999999</v>
       </c>
       <c r="N87" t="n">
-        <v>83.5</v>
+        <v>62.3</v>
       </c>
       <c r="O87" t="inlineStr">
         <is>
@@ -5633,7 +5629,7 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -5662,30 +5658,30 @@
         <v>2</v>
       </c>
       <c r="G88" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Mister Winston</t>
+          <t>War Socks</t>
         </is>
       </c>
       <c r="I88" t="n">
         <v>4</v>
       </c>
       <c r="J88" t="n">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="K88" t="n">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="L88" t="n">
-        <v>11.98</v>
+        <v>16.78</v>
       </c>
       <c r="M88" t="n">
         <v>99.23999999999999</v>
       </c>
       <c r="N88" t="n">
-        <v>68</v>
+        <v>53.9</v>
       </c>
       <c r="O88" t="inlineStr">
         <is>
@@ -5693,7 +5689,7 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="89">
@@ -5722,30 +5718,30 @@
         <v>2</v>
       </c>
       <c r="G89" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Skukuza</t>
+          <t>Urban Lion</t>
         </is>
       </c>
       <c r="I89" t="n">
         <v>5</v>
       </c>
       <c r="J89" t="n">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="K89" t="n">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="L89" t="n">
-        <v>16.73</v>
+        <v>17.28</v>
       </c>
       <c r="M89" t="n">
         <v>99.23999999999999</v>
       </c>
       <c r="N89" t="n">
-        <v>62.3</v>
+        <v>53.9</v>
       </c>
       <c r="O89" t="inlineStr">
         <is>
@@ -5753,7 +5749,7 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="90">
@@ -5782,11 +5778,11 @@
         <v>2</v>
       </c>
       <c r="G90" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>War Socks</t>
+          <t>Excellent Believe</t>
         </is>
       </c>
       <c r="I90" t="n">
@@ -5796,16 +5792,16 @@
         <v>127</v>
       </c>
       <c r="K90" t="n">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="L90" t="n">
-        <v>16.78</v>
+        <v>17.38000000000001</v>
       </c>
       <c r="M90" t="n">
         <v>99.23999999999999</v>
       </c>
       <c r="N90" t="n">
-        <v>53.9</v>
+        <v>51.9</v>
       </c>
       <c r="O90" t="inlineStr">
         <is>
@@ -5813,7 +5809,7 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>-1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -5842,30 +5838,30 @@
         <v>2</v>
       </c>
       <c r="G91" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Urban Lion</t>
+          <t>One Smack Mac (IRE)</t>
         </is>
       </c>
       <c r="I91" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J91" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="K91" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L91" t="n">
-        <v>17.28</v>
+        <v>19.88</v>
       </c>
       <c r="M91" t="n">
         <v>99.23999999999999</v>
       </c>
       <c r="N91" t="n">
-        <v>53.9</v>
+        <v>47.7</v>
       </c>
       <c r="O91" t="inlineStr">
         <is>
@@ -5873,7 +5869,7 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -5901,40 +5897,24 @@
       <c r="F92" t="n">
         <v>2</v>
       </c>
-      <c r="G92" t="n">
-        <v>27</v>
-      </c>
+      <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Excellent Believe</t>
-        </is>
-      </c>
-      <c r="I92" t="n">
-        <v>4</v>
-      </c>
-      <c r="J92" t="n">
-        <v>134</v>
-      </c>
-      <c r="K92" t="n">
-        <v>106</v>
-      </c>
-      <c r="L92" t="n">
-        <v>17.38</v>
-      </c>
-      <c r="M92" t="n">
-        <v>99.23999999999999</v>
-      </c>
-      <c r="N92" t="n">
-        <v>59.2</v>
-      </c>
+          <t>Chibitty (FR)</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P92" t="n">
-        <v>2</v>
-      </c>
+      <c r="P92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5961,40 +5941,24 @@
       <c r="F93" t="n">
         <v>2</v>
       </c>
-      <c r="G93" t="n">
-        <v>28</v>
-      </c>
+      <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr">
         <is>
-          <t>One Smack Mac (IRE)</t>
-        </is>
-      </c>
-      <c r="I93" t="n">
-        <v>4</v>
-      </c>
-      <c r="J93" t="n">
-        <v>129</v>
-      </c>
-      <c r="K93" t="n">
-        <v>101</v>
-      </c>
-      <c r="L93" t="n">
-        <v>19.88</v>
-      </c>
-      <c r="M93" t="n">
-        <v>99.23999999999999</v>
-      </c>
-      <c r="N93" t="n">
-        <v>47.7</v>
-      </c>
+          <t>Linwood (IRE)</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P93" t="n">
-        <v>0</v>
-      </c>
+      <c r="P93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -6022,34 +5986,36 @@
         <v>2</v>
       </c>
       <c r="G94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Song N Dance</t>
+          <t>Alobayyah</t>
         </is>
       </c>
       <c r="I94" t="n">
         <v>4</v>
       </c>
       <c r="J94" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="K94" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="n">
         <v>99.31</v>
       </c>
-      <c r="N94" t="inlineStr"/>
+      <c r="N94" t="n">
+        <v>93</v>
+      </c>
       <c r="O94" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P94" t="n">
-        <v>-25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -6078,28 +6044,30 @@
         <v>2</v>
       </c>
       <c r="G95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Alobayyah</t>
+          <t>Miss Nightfall</t>
         </is>
       </c>
       <c r="I95" t="n">
         <v>4</v>
       </c>
       <c r="J95" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K95" t="n">
-        <v>90</v>
-      </c>
-      <c r="L95" t="inlineStr"/>
+        <v>89</v>
+      </c>
+      <c r="L95" t="n">
+        <v>0.15</v>
+      </c>
       <c r="M95" t="n">
         <v>99.31</v>
       </c>
       <c r="N95" t="n">
-        <v>93</v>
+        <v>89.7</v>
       </c>
       <c r="O95" t="inlineStr">
         <is>
@@ -6136,30 +6104,30 @@
         <v>2</v>
       </c>
       <c r="G96" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Miss Nightfall</t>
+          <t>Seren Star (IRE)</t>
         </is>
       </c>
       <c r="I96" t="n">
         <v>4</v>
       </c>
       <c r="J96" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="K96" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L96" t="n">
-        <v>0.15</v>
+        <v>0.65</v>
       </c>
       <c r="M96" t="n">
         <v>99.31</v>
       </c>
       <c r="N96" t="n">
-        <v>89.7</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="O96" t="inlineStr">
         <is>
@@ -6167,7 +6135,7 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="97">
@@ -6196,30 +6164,30 @@
         <v>2</v>
       </c>
       <c r="G97" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Seren Star (IRE)</t>
+          <t>Rhapsody (IRE)</t>
         </is>
       </c>
       <c r="I97" t="n">
         <v>4</v>
       </c>
       <c r="J97" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="K97" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="L97" t="n">
-        <v>0.65</v>
+        <v>2.15</v>
       </c>
       <c r="M97" t="n">
         <v>99.31</v>
       </c>
       <c r="N97" t="n">
-        <v>88.40000000000001</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="O97" t="inlineStr">
         <is>
@@ -6227,7 +6195,7 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -6256,30 +6224,30 @@
         <v>2</v>
       </c>
       <c r="G98" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Rhapsody (IRE)</t>
+          <t>Rumba Numba</t>
         </is>
       </c>
       <c r="I98" t="n">
         <v>4</v>
       </c>
       <c r="J98" t="n">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="K98" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="L98" t="n">
-        <v>2.15</v>
+        <v>2.65</v>
       </c>
       <c r="M98" t="n">
         <v>99.31</v>
       </c>
       <c r="N98" t="n">
-        <v>88.90000000000001</v>
+        <v>85.2</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
@@ -6287,7 +6255,7 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="99">
@@ -6316,30 +6284,30 @@
         <v>2</v>
       </c>
       <c r="G99" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Rumba Numba</t>
+          <t>Quamby (IRE)</t>
         </is>
       </c>
       <c r="I99" t="n">
         <v>4</v>
       </c>
       <c r="J99" t="n">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="K99" t="n">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="L99" t="n">
-        <v>2.65</v>
+        <v>3.15</v>
       </c>
       <c r="M99" t="n">
         <v>99.31</v>
       </c>
       <c r="N99" t="n">
-        <v>85.2</v>
+        <v>78</v>
       </c>
       <c r="O99" t="inlineStr">
         <is>
@@ -6347,7 +6315,7 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>-3</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="100">
@@ -6376,30 +6344,30 @@
         <v>2</v>
       </c>
       <c r="G100" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Quamby (IRE)</t>
+          <t>Callianassa (IRE)</t>
         </is>
       </c>
       <c r="I100" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J100" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K100" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="L100" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="M100" t="n">
         <v>99.31</v>
       </c>
       <c r="N100" t="n">
-        <v>78</v>
+        <v>78.2</v>
       </c>
       <c r="O100" t="inlineStr">
         <is>
@@ -6407,7 +6375,7 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="101">
@@ -6436,30 +6404,30 @@
         <v>2</v>
       </c>
       <c r="G101" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Callianassa (IRE)</t>
+          <t>Cheshire Dancer (IRE)</t>
         </is>
       </c>
       <c r="I101" t="n">
         <v>5</v>
       </c>
       <c r="J101" t="n">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="K101" t="n">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="L101" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="M101" t="n">
         <v>99.31</v>
       </c>
       <c r="N101" t="n">
-        <v>78.2</v>
+        <v>89.5</v>
       </c>
       <c r="O101" t="inlineStr">
         <is>
@@ -6467,7 +6435,7 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>-3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="102">
@@ -6496,30 +6464,30 @@
         <v>2</v>
       </c>
       <c r="G102" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Cheshire Dancer (IRE)</t>
+          <t>Gaga Girl (FR)</t>
         </is>
       </c>
       <c r="I102" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J102" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="K102" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="L102" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="M102" t="n">
         <v>99.31</v>
       </c>
       <c r="N102" t="n">
-        <v>89.5</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="O102" t="inlineStr">
         <is>
@@ -6527,7 +6495,7 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="103">
@@ -6556,11 +6524,11 @@
         <v>2</v>
       </c>
       <c r="G103" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Gaga Girl (FR)</t>
+          <t>American Gal</t>
         </is>
       </c>
       <c r="I103" t="n">
@@ -6573,13 +6541,13 @@
         <v>97</v>
       </c>
       <c r="L103" t="n">
-        <v>3.9</v>
+        <v>4.9</v>
       </c>
       <c r="M103" t="n">
         <v>99.31</v>
       </c>
       <c r="N103" t="n">
-        <v>88.09999999999999</v>
+        <v>87.3</v>
       </c>
       <c r="O103" t="inlineStr">
         <is>
@@ -6616,30 +6584,30 @@
         <v>2</v>
       </c>
       <c r="G104" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>American Gal</t>
+          <t>Crystal Flyer</t>
         </is>
       </c>
       <c r="I104" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J104" t="n">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="K104" t="n">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="L104" t="n">
-        <v>4.9</v>
+        <v>5.65</v>
       </c>
       <c r="M104" t="n">
         <v>99.31</v>
       </c>
       <c r="N104" t="n">
-        <v>87.3</v>
+        <v>75.3</v>
       </c>
       <c r="O104" t="inlineStr">
         <is>
@@ -6647,7 +6615,7 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="105">
@@ -6676,15 +6644,15 @@
         <v>2</v>
       </c>
       <c r="G105" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Crystal Flyer</t>
+          <t>Zgharta (IRE)</t>
         </is>
       </c>
       <c r="I105" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J105" t="n">
         <v>121</v>
@@ -6693,13 +6661,13 @@
         <v>88</v>
       </c>
       <c r="L105" t="n">
-        <v>5.65</v>
+        <v>6.15</v>
       </c>
       <c r="M105" t="n">
         <v>99.31</v>
       </c>
       <c r="N105" t="n">
-        <v>75.3</v>
+        <v>75.2</v>
       </c>
       <c r="O105" t="inlineStr">
         <is>
@@ -6736,30 +6704,30 @@
         <v>2</v>
       </c>
       <c r="G106" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Zgharta (IRE)</t>
+          <t>Radiant Beauty</t>
         </is>
       </c>
       <c r="I106" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J106" t="n">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="K106" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="L106" t="n">
-        <v>6.15</v>
+        <v>6.9</v>
       </c>
       <c r="M106" t="n">
         <v>99.31</v>
       </c>
       <c r="N106" t="n">
-        <v>75.2</v>
+        <v>77.7</v>
       </c>
       <c r="O106" t="inlineStr">
         <is>
@@ -6767,7 +6735,7 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
@@ -6796,30 +6764,30 @@
         <v>2</v>
       </c>
       <c r="G107" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Radiant Beauty</t>
+          <t>Goldilocks Cen</t>
         </is>
       </c>
       <c r="I107" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J107" t="n">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="K107" t="n">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="L107" t="n">
-        <v>6.9</v>
+        <v>6.95</v>
       </c>
       <c r="M107" t="n">
         <v>99.31</v>
       </c>
       <c r="N107" t="n">
-        <v>77.7</v>
+        <v>68.8</v>
       </c>
       <c r="O107" t="inlineStr">
         <is>
@@ -6827,7 +6795,7 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="108">
@@ -6856,30 +6824,30 @@
         <v>2</v>
       </c>
       <c r="G108" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Goldilocks Cen</t>
+          <t>All Moonshine</t>
         </is>
       </c>
       <c r="I108" t="n">
         <v>4</v>
       </c>
       <c r="J108" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="K108" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="L108" t="n">
-        <v>6.95</v>
+        <v>7.05</v>
       </c>
       <c r="M108" t="n">
         <v>99.31</v>
       </c>
       <c r="N108" t="n">
-        <v>68.8</v>
+        <v>72.3</v>
       </c>
       <c r="O108" t="inlineStr">
         <is>
@@ -6887,7 +6855,7 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -6916,30 +6884,30 @@
         <v>2</v>
       </c>
       <c r="G109" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>All Moonshine</t>
+          <t>Sand Gazelle</t>
         </is>
       </c>
       <c r="I109" t="n">
         <v>4</v>
       </c>
       <c r="J109" t="n">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="K109" t="n">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="L109" t="n">
-        <v>7.05</v>
+        <v>7.2</v>
       </c>
       <c r="M109" t="n">
         <v>99.31</v>
       </c>
       <c r="N109" t="n">
-        <v>72.3</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="O109" t="inlineStr">
         <is>
@@ -6947,7 +6915,7 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="110">
@@ -6976,30 +6944,30 @@
         <v>2</v>
       </c>
       <c r="G110" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Sand Gazelle</t>
+          <t>Unassuming (FR)</t>
         </is>
       </c>
       <c r="I110" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J110" t="n">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="K110" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="L110" t="n">
-        <v>7.2</v>
+        <v>8.950000000000001</v>
       </c>
       <c r="M110" t="n">
         <v>99.31</v>
       </c>
       <c r="N110" t="n">
-        <v>82.59999999999999</v>
+        <v>68.3</v>
       </c>
       <c r="O110" t="inlineStr">
         <is>
@@ -7007,7 +6975,7 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -7036,30 +7004,30 @@
         <v>2</v>
       </c>
       <c r="G111" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Unassuming (FR)</t>
+          <t>Lady Mariko</t>
         </is>
       </c>
       <c r="I111" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J111" t="n">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="K111" t="n">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="L111" t="n">
-        <v>8.949999999999999</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="M111" t="n">
         <v>99.31</v>
       </c>
       <c r="N111" t="n">
-        <v>68.3</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="O111" t="inlineStr">
         <is>
@@ -7067,7 +7035,7 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="112">
@@ -7096,30 +7064,30 @@
         <v>2</v>
       </c>
       <c r="G112" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Lady Mariko</t>
+          <t>Muddy Mooy (IRE)</t>
         </is>
       </c>
       <c r="I112" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J112" t="n">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="K112" t="n">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="L112" t="n">
-        <v>9.449999999999999</v>
+        <v>13.2</v>
       </c>
       <c r="M112" t="n">
         <v>99.31</v>
       </c>
       <c r="N112" t="n">
-        <v>64.40000000000001</v>
+        <v>68</v>
       </c>
       <c r="O112" t="inlineStr">
         <is>
@@ -7127,7 +7095,7 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
@@ -7156,30 +7124,30 @@
         <v>2</v>
       </c>
       <c r="G113" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Muddy Mooy (IRE)</t>
+          <t>Oolong Poobong (IRE)</t>
         </is>
       </c>
       <c r="I113" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J113" t="n">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="K113" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="L113" t="n">
-        <v>13.2</v>
+        <v>17.45</v>
       </c>
       <c r="M113" t="n">
         <v>99.31</v>
       </c>
       <c r="N113" t="n">
-        <v>68</v>
+        <v>42.7</v>
       </c>
       <c r="O113" t="inlineStr">
         <is>
@@ -7187,7 +7155,7 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="114">
@@ -7216,38 +7184,38 @@
         <v>2</v>
       </c>
       <c r="G114" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Oolong Poobong (IRE)</t>
+          <t>Stateira (FR)</t>
         </is>
       </c>
       <c r="I114" t="n">
         <v>4</v>
       </c>
       <c r="J114" t="n">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="K114" t="n">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="L114" t="n">
-        <v>17.45</v>
+        <v>21.7</v>
       </c>
       <c r="M114" t="n">
         <v>99.31</v>
       </c>
       <c r="N114" t="n">
-        <v>42.7</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="P114" t="n">
-        <v>-3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="115">
@@ -7276,30 +7244,30 @@
         <v>2</v>
       </c>
       <c r="G115" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Stateira (FR)</t>
+          <t>Perfect Part (IRE)</t>
         </is>
       </c>
       <c r="I115" t="n">
         <v>4</v>
       </c>
       <c r="J115" t="n">
-        <v>138</v>
+        <v>119</v>
       </c>
       <c r="K115" t="n">
-        <v>105</v>
+        <v>86</v>
       </c>
       <c r="L115" t="n">
-        <v>21.7</v>
+        <v>22.2</v>
       </c>
       <c r="M115" t="n">
         <v>99.31</v>
       </c>
       <c r="N115" t="n">
-        <v>65.09999999999999</v>
+        <v>47.7</v>
       </c>
       <c r="O115" t="inlineStr">
         <is>
@@ -7307,7 +7275,7 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -7336,30 +7304,30 @@
         <v>2</v>
       </c>
       <c r="G116" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Perfect Part (IRE)</t>
+          <t>Betty Clover</t>
         </is>
       </c>
       <c r="I116" t="n">
         <v>4</v>
       </c>
       <c r="J116" t="n">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="K116" t="n">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="L116" t="n">
-        <v>22.2</v>
+        <v>30.7</v>
       </c>
       <c r="M116" t="n">
         <v>99.31</v>
       </c>
       <c r="N116" t="n">
-        <v>47.7</v>
+        <v>49.5</v>
       </c>
       <c r="O116" t="inlineStr">
         <is>
@@ -7367,7 +7335,7 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="117">
@@ -7396,30 +7364,30 @@
         <v>2</v>
       </c>
       <c r="G117" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Betty Clover</t>
+          <t>Renesmee</t>
         </is>
       </c>
       <c r="I117" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J117" t="n">
-        <v>128</v>
+        <v>107</v>
       </c>
       <c r="K117" t="n">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="L117" t="n">
-        <v>30.7</v>
+        <v>34.7</v>
       </c>
       <c r="M117" t="n">
         <v>99.31</v>
       </c>
       <c r="N117" t="n">
-        <v>49.5</v>
+        <v>34.6</v>
       </c>
       <c r="O117" t="inlineStr">
         <is>
@@ -7427,7 +7395,7 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -7455,40 +7423,24 @@
       <c r="F118" t="n">
         <v>2</v>
       </c>
-      <c r="G118" t="n">
-        <v>24</v>
-      </c>
+      <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Renesmee</t>
-        </is>
-      </c>
-      <c r="I118" t="n">
-        <v>6</v>
-      </c>
-      <c r="J118" t="n">
-        <v>114</v>
-      </c>
-      <c r="K118" t="n">
-        <v>81</v>
-      </c>
-      <c r="L118" t="n">
-        <v>34.7</v>
-      </c>
-      <c r="M118" t="n">
-        <v>99.31</v>
-      </c>
-      <c r="N118" t="n">
-        <v>34.5</v>
-      </c>
+          <t>Song N Dance</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
       <c r="O118" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="P118" t="n">
-        <v>0</v>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -8251,7 +8203,7 @@
         <v>0</v>
       </c>
       <c r="L131" t="n">
-        <v>5.2</v>
+        <v>5.199999999999999</v>
       </c>
       <c r="M131" t="n">
         <v>73.34</v>
@@ -8311,7 +8263,7 @@
         <v>0</v>
       </c>
       <c r="L132" t="n">
-        <v>5.95</v>
+        <v>5.949999999999999</v>
       </c>
       <c r="M132" t="n">
         <v>73.34</v>
@@ -8371,7 +8323,7 @@
         <v>0</v>
       </c>
       <c r="L133" t="n">
-        <v>6.45</v>
+        <v>6.449999999999999</v>
       </c>
       <c r="M133" t="n">
         <v>73.34</v>
@@ -8431,7 +8383,7 @@
         <v>0</v>
       </c>
       <c r="L134" t="n">
-        <v>6.95</v>
+        <v>6.949999999999999</v>
       </c>
       <c r="M134" t="n">
         <v>73.34</v>
@@ -9014,34 +8966,36 @@
         <v>6</v>
       </c>
       <c r="G144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Bridgets Baby</t>
+          <t>Sonic Si</t>
         </is>
       </c>
       <c r="I144" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J144" t="n">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="K144" t="n">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" t="n">
         <v>61.26</v>
       </c>
-      <c r="N144" t="inlineStr"/>
+      <c r="N144" t="n">
+        <v>59.1</v>
+      </c>
       <c r="O144" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P144" t="n">
-        <v>-5.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145">
@@ -9070,34 +9024,38 @@
         <v>6</v>
       </c>
       <c r="G145" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Hallandale Beach</t>
+          <t>Level Up (IRE)</t>
         </is>
       </c>
       <c r="I145" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J145" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="K145" t="n">
-        <v>64</v>
-      </c>
-      <c r="L145" t="inlineStr"/>
+        <v>63</v>
+      </c>
+      <c r="L145" t="n">
+        <v>1.5</v>
+      </c>
       <c r="M145" t="n">
         <v>61.26</v>
       </c>
-      <c r="N145" t="inlineStr"/>
+      <c r="N145" t="n">
+        <v>51.6</v>
+      </c>
       <c r="O145" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P145" t="n">
-        <v>-5.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
@@ -9126,28 +9084,30 @@
         <v>6</v>
       </c>
       <c r="G146" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Sonic Si</t>
+          <t>So Smart (IRE)</t>
         </is>
       </c>
       <c r="I146" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J146" t="n">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="K146" t="n">
-        <v>66</v>
-      </c>
-      <c r="L146" t="inlineStr"/>
+        <v>59</v>
+      </c>
+      <c r="L146" t="n">
+        <v>5.5</v>
+      </c>
       <c r="M146" t="n">
         <v>61.26</v>
       </c>
       <c r="N146" t="n">
-        <v>63.6</v>
+        <v>38.2</v>
       </c>
       <c r="O146" t="inlineStr">
         <is>
@@ -9184,30 +9144,30 @@
         <v>6</v>
       </c>
       <c r="G147" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Level Up (IRE)</t>
+          <t>Vape</t>
         </is>
       </c>
       <c r="I147" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J147" t="n">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="K147" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="L147" t="n">
-        <v>1.5</v>
+        <v>10</v>
       </c>
       <c r="M147" t="n">
         <v>61.26</v>
       </c>
       <c r="N147" t="n">
-        <v>56.4</v>
+        <v>22.1</v>
       </c>
       <c r="O147" t="inlineStr">
         <is>
@@ -9243,40 +9203,24 @@
       <c r="F148" t="n">
         <v>6</v>
       </c>
-      <c r="G148" t="n">
-        <v>3</v>
-      </c>
+      <c r="G148" t="inlineStr"/>
       <c r="H148" t="inlineStr">
         <is>
-          <t>So Smart (IRE)</t>
-        </is>
-      </c>
-      <c r="I148" t="n">
-        <v>7</v>
-      </c>
-      <c r="J148" t="n">
-        <v>136</v>
-      </c>
-      <c r="K148" t="n">
-        <v>59</v>
-      </c>
-      <c r="L148" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="M148" t="n">
-        <v>61.26</v>
-      </c>
-      <c r="N148" t="n">
-        <v>40.4</v>
-      </c>
+          <t>Bridgets Baby</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr"/>
+      <c r="N148" t="inlineStr"/>
       <c r="O148" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P148" t="n">
-        <v>0</v>
-      </c>
+      <c r="P148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -9303,40 +9247,24 @@
       <c r="F149" t="n">
         <v>6</v>
       </c>
-      <c r="G149" t="n">
-        <v>4</v>
-      </c>
+      <c r="G149" t="inlineStr"/>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Vape</t>
-        </is>
-      </c>
-      <c r="I149" t="n">
-        <v>9</v>
-      </c>
-      <c r="J149" t="n">
-        <v>138</v>
-      </c>
-      <c r="K149" t="n">
-        <v>61</v>
-      </c>
-      <c r="L149" t="n">
-        <v>10</v>
-      </c>
-      <c r="M149" t="n">
-        <v>61.26</v>
-      </c>
-      <c r="N149" t="n">
-        <v>28.8</v>
-      </c>
+          <t>Hallandale Beach</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" t="inlineStr"/>
+      <c r="N149" t="inlineStr"/>
       <c r="O149" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P149" t="n">
-        <v>0</v>
-      </c>
+      <c r="P149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -9364,18 +9292,18 @@
         <v>5</v>
       </c>
       <c r="G150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Leading Raya (IRE)</t>
+          <t>Tango Hotel</t>
         </is>
       </c>
       <c r="I150" t="n">
         <v>2</v>
       </c>
       <c r="J150" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="K150" t="n">
         <v>0</v>
@@ -9384,14 +9312,16 @@
       <c r="M150" t="n">
         <v>61.77</v>
       </c>
-      <c r="N150" t="inlineStr"/>
+      <c r="N150" t="n">
+        <v>62.5</v>
+      </c>
       <c r="O150" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P150" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151">
@@ -9420,28 +9350,30 @@
         <v>5</v>
       </c>
       <c r="G151" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Tango Hotel</t>
+          <t>Defiant Dream</t>
         </is>
       </c>
       <c r="I151" t="n">
         <v>2</v>
       </c>
       <c r="J151" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="K151" t="n">
         <v>0</v>
       </c>
-      <c r="L151" t="inlineStr"/>
+      <c r="L151" t="n">
+        <v>2.25</v>
+      </c>
       <c r="M151" t="n">
         <v>61.77</v>
       </c>
       <c r="N151" t="n">
-        <v>65.8</v>
+        <v>55.7</v>
       </c>
       <c r="O151" t="inlineStr">
         <is>
@@ -9478,11 +9410,11 @@
         <v>5</v>
       </c>
       <c r="G152" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Defiant Dream</t>
+          <t>Past Passion</t>
         </is>
       </c>
       <c r="I152" t="n">
@@ -9495,13 +9427,13 @@
         <v>0</v>
       </c>
       <c r="L152" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="M152" t="n">
         <v>61.77</v>
       </c>
       <c r="N152" t="n">
-        <v>55.7</v>
+        <v>53.9</v>
       </c>
       <c r="O152" t="inlineStr">
         <is>
@@ -9509,7 +9441,7 @@
         </is>
       </c>
       <c r="P152" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="153">
@@ -9538,30 +9470,30 @@
         <v>5</v>
       </c>
       <c r="G153" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Past Passion</t>
+          <t>Cavan Lady</t>
         </is>
       </c>
       <c r="I153" t="n">
         <v>2</v>
       </c>
       <c r="J153" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="K153" t="n">
         <v>0</v>
       </c>
       <c r="L153" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="M153" t="n">
         <v>61.77</v>
       </c>
       <c r="N153" t="n">
-        <v>53.9</v>
+        <v>54.4</v>
       </c>
       <c r="O153" t="inlineStr">
         <is>
@@ -9569,7 +9501,7 @@
         </is>
       </c>
       <c r="P153" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154">
@@ -9598,11 +9530,11 @@
         <v>5</v>
       </c>
       <c r="G154" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Cavan Lady</t>
+          <t>Nasserein (IRE)</t>
         </is>
       </c>
       <c r="I154" t="n">
@@ -9615,13 +9547,13 @@
         <v>0</v>
       </c>
       <c r="L154" t="n">
-        <v>2.55</v>
+        <v>5.550000000000001</v>
       </c>
       <c r="M154" t="n">
         <v>61.77</v>
       </c>
       <c r="N154" t="n">
-        <v>54.4</v>
+        <v>42.9</v>
       </c>
       <c r="O154" t="inlineStr">
         <is>
@@ -9629,7 +9561,7 @@
         </is>
       </c>
       <c r="P154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155">
@@ -9657,40 +9589,24 @@
       <c r="F155" t="n">
         <v>5</v>
       </c>
-      <c r="G155" t="n">
-        <v>5</v>
-      </c>
+      <c r="G155" t="inlineStr"/>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Nasserein (IRE)</t>
-        </is>
-      </c>
-      <c r="I155" t="n">
-        <v>2</v>
-      </c>
-      <c r="J155" t="n">
-        <v>128</v>
-      </c>
-      <c r="K155" t="n">
-        <v>0</v>
-      </c>
-      <c r="L155" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="M155" t="n">
-        <v>61.77</v>
-      </c>
-      <c r="N155" t="n">
-        <v>42.9</v>
-      </c>
+          <t>Leading Raya (IRE)</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" t="inlineStr"/>
+      <c r="N155" t="inlineStr"/>
       <c r="O155" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P155" t="n">
-        <v>0</v>
-      </c>
+      <c r="P155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -9718,34 +9634,36 @@
         <v>6</v>
       </c>
       <c r="G156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Who Is Alice</t>
+          <t>Gelato (IRE)</t>
         </is>
       </c>
       <c r="I156" t="n">
         <v>3</v>
       </c>
       <c r="J156" t="n">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="K156" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="L156" t="inlineStr"/>
       <c r="M156" t="n">
         <v>97.37</v>
       </c>
-      <c r="N156" t="inlineStr"/>
+      <c r="N156" t="n">
+        <v>42</v>
+      </c>
       <c r="O156" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P156" t="n">
-        <v>-8.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157">
@@ -9774,34 +9692,38 @@
         <v>6</v>
       </c>
       <c r="G157" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Thai Princess</t>
+          <t>Senor Campanaro (IRE)</t>
         </is>
       </c>
       <c r="I157" t="n">
         <v>3</v>
       </c>
       <c r="J157" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="K157" t="n">
-        <v>60</v>
-      </c>
-      <c r="L157" t="inlineStr"/>
+        <v>64</v>
+      </c>
+      <c r="L157" t="n">
+        <v>3</v>
+      </c>
       <c r="M157" t="n">
         <v>97.37</v>
       </c>
-      <c r="N157" t="inlineStr"/>
+      <c r="N157" t="n">
+        <v>39.9</v>
+      </c>
       <c r="O157" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P157" t="n">
-        <v>-8.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158">
@@ -9830,28 +9752,30 @@
         <v>6</v>
       </c>
       <c r="G158" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Gelato (IRE)</t>
+          <t>Red Moon (IRE)</t>
         </is>
       </c>
       <c r="I158" t="n">
         <v>3</v>
       </c>
       <c r="J158" t="n">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="K158" t="n">
-        <v>59</v>
-      </c>
-      <c r="L158" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="L158" t="n">
+        <v>4.5</v>
+      </c>
       <c r="M158" t="n">
         <v>97.37</v>
       </c>
       <c r="N158" t="n">
-        <v>45.4</v>
+        <v>30.9</v>
       </c>
       <c r="O158" t="inlineStr">
         <is>
@@ -9888,30 +9812,30 @@
         <v>6</v>
       </c>
       <c r="G159" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Senor Campanaro (IRE)</t>
+          <t>Distillation (FR)</t>
         </is>
       </c>
       <c r="I159" t="n">
         <v>3</v>
       </c>
       <c r="J159" t="n">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="K159" t="n">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="L159" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M159" t="n">
         <v>97.37</v>
       </c>
       <c r="N159" t="n">
-        <v>42.8</v>
+        <v>27.6</v>
       </c>
       <c r="O159" t="inlineStr">
         <is>
@@ -9919,7 +9843,7 @@
         </is>
       </c>
       <c r="P159" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="160">
@@ -9948,30 +9872,30 @@
         <v>6</v>
       </c>
       <c r="G160" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Red Moon (IRE)</t>
+          <t>Phantom Shadow (FR)</t>
         </is>
       </c>
       <c r="I160" t="n">
         <v>3</v>
       </c>
       <c r="J160" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="K160" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="L160" t="n">
-        <v>4.5</v>
+        <v>6.25</v>
       </c>
       <c r="M160" t="n">
         <v>97.37</v>
       </c>
       <c r="N160" t="n">
-        <v>38.3</v>
+        <v>27.6</v>
       </c>
       <c r="O160" t="inlineStr">
         <is>
@@ -9979,7 +9903,7 @@
         </is>
       </c>
       <c r="P160" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="161">
@@ -10008,30 +9932,30 @@
         <v>6</v>
       </c>
       <c r="G161" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Distillation (FR)</t>
+          <t>Katies Song</t>
         </is>
       </c>
       <c r="I161" t="n">
         <v>3</v>
       </c>
       <c r="J161" t="n">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="K161" t="n">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="L161" t="n">
-        <v>5</v>
+        <v>13.75</v>
       </c>
       <c r="M161" t="n">
         <v>97.37</v>
       </c>
       <c r="N161" t="n">
-        <v>27.6</v>
+        <v>10.6</v>
       </c>
       <c r="O161" t="inlineStr">
         <is>
@@ -10039,7 +9963,7 @@
         </is>
       </c>
       <c r="P161" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162">
@@ -10068,30 +9992,30 @@
         <v>6</v>
       </c>
       <c r="G162" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Phantom Shadow (FR)</t>
+          <t>Kingofthecarnival (FR)</t>
         </is>
       </c>
       <c r="I162" t="n">
         <v>3</v>
       </c>
       <c r="J162" t="n">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="K162" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="L162" t="n">
-        <v>6.25</v>
+        <v>15.25</v>
       </c>
       <c r="M162" t="n">
         <v>97.37</v>
       </c>
       <c r="N162" t="n">
-        <v>27.6</v>
+        <v>-18.6</v>
       </c>
       <c r="O162" t="inlineStr">
         <is>
@@ -10099,7 +10023,7 @@
         </is>
       </c>
       <c r="P162" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="163">
@@ -10127,40 +10051,24 @@
       <c r="F163" t="n">
         <v>6</v>
       </c>
-      <c r="G163" t="n">
-        <v>6</v>
-      </c>
+      <c r="G163" t="inlineStr"/>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Katies Song</t>
-        </is>
-      </c>
-      <c r="I163" t="n">
-        <v>3</v>
-      </c>
-      <c r="J163" t="n">
-        <v>135</v>
-      </c>
-      <c r="K163" t="n">
-        <v>64</v>
-      </c>
-      <c r="L163" t="n">
-        <v>13.75</v>
-      </c>
-      <c r="M163" t="n">
-        <v>97.37</v>
-      </c>
-      <c r="N163" t="n">
-        <v>10.6</v>
-      </c>
+          <t>Thai Princess</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr"/>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" t="inlineStr"/>
+      <c r="N163" t="inlineStr"/>
       <c r="O163" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P163" t="n">
-        <v>0</v>
-      </c>
+      <c r="P163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -10187,40 +10095,24 @@
       <c r="F164" t="n">
         <v>6</v>
       </c>
-      <c r="G164" t="n">
-        <v>7</v>
-      </c>
+      <c r="G164" t="inlineStr"/>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Kingofthecarnival (FR)</t>
-        </is>
-      </c>
-      <c r="I164" t="n">
-        <v>3</v>
-      </c>
-      <c r="J164" t="n">
-        <v>132</v>
-      </c>
-      <c r="K164" t="n">
-        <v>61</v>
-      </c>
-      <c r="L164" t="n">
-        <v>15.25</v>
-      </c>
-      <c r="M164" t="n">
-        <v>97.37</v>
-      </c>
-      <c r="N164" t="n">
-        <v>-1.7</v>
-      </c>
+          <t>Who Is Alice</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
+      <c r="K164" t="inlineStr"/>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" t="inlineStr"/>
+      <c r="N164" t="inlineStr"/>
       <c r="O164" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P164" t="n">
-        <v>0</v>
-      </c>
+      <c r="P164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -10248,34 +10140,36 @@
         <v>4</v>
       </c>
       <c r="G165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Huscal (IRE)</t>
+          <t>Great Dream</t>
         </is>
       </c>
       <c r="I165" t="n">
         <v>4</v>
       </c>
       <c r="J165" t="n">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="K165" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="L165" t="inlineStr"/>
       <c r="M165" t="n">
         <v>95.12</v>
       </c>
-      <c r="N165" t="inlineStr"/>
+      <c r="N165" t="n">
+        <v>75.90000000000001</v>
+      </c>
       <c r="O165" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P165" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166">
@@ -10304,28 +10198,30 @@
         <v>4</v>
       </c>
       <c r="G166" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Great Dream</t>
+          <t>Sunny Smile (IRE)</t>
         </is>
       </c>
       <c r="I166" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J166" t="n">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="K166" t="n">
-        <v>80</v>
-      </c>
-      <c r="L166" t="inlineStr"/>
+        <v>81</v>
+      </c>
+      <c r="L166" t="n">
+        <v>11</v>
+      </c>
       <c r="M166" t="n">
         <v>95.12</v>
       </c>
       <c r="N166" t="n">
-        <v>75.90000000000001</v>
+        <v>45.6</v>
       </c>
       <c r="O166" t="inlineStr">
         <is>
@@ -10333,7 +10229,7 @@
         </is>
       </c>
       <c r="P166" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="167">
@@ -10362,30 +10258,30 @@
         <v>4</v>
       </c>
       <c r="G167" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Sunny Smile (IRE)</t>
+          <t>Factual (IRE)</t>
         </is>
       </c>
       <c r="I167" t="n">
         <v>3</v>
       </c>
       <c r="J167" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="K167" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="L167" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="M167" t="n">
         <v>95.12</v>
       </c>
       <c r="N167" t="n">
-        <v>45.6</v>
+        <v>49.3</v>
       </c>
       <c r="O167" t="inlineStr">
         <is>
@@ -10393,7 +10289,7 @@
         </is>
       </c>
       <c r="P167" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="168">
@@ -10422,30 +10318,30 @@
         <v>4</v>
       </c>
       <c r="G168" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Factual (IRE)</t>
+          <t>Slight Of Foot</t>
         </is>
       </c>
       <c r="I168" t="n">
         <v>3</v>
       </c>
       <c r="J168" t="n">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="K168" t="n">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="L168" t="n">
-        <v>11.1</v>
+        <v>11.6</v>
       </c>
       <c r="M168" t="n">
         <v>95.12</v>
       </c>
       <c r="N168" t="n">
-        <v>49.3</v>
+        <v>40.3</v>
       </c>
       <c r="O168" t="inlineStr">
         <is>
@@ -10453,7 +10349,7 @@
         </is>
       </c>
       <c r="P168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="169">
@@ -10482,30 +10378,30 @@
         <v>4</v>
       </c>
       <c r="G169" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Slight Of Foot</t>
+          <t>Marlborough Place (IRE)</t>
         </is>
       </c>
       <c r="I169" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J169" t="n">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="K169" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="L169" t="n">
-        <v>11.6</v>
+        <v>17.1</v>
       </c>
       <c r="M169" t="n">
         <v>95.12</v>
       </c>
       <c r="N169" t="n">
-        <v>40.3</v>
+        <v>33.1</v>
       </c>
       <c r="O169" t="inlineStr">
         <is>
@@ -10542,30 +10438,30 @@
         <v>4</v>
       </c>
       <c r="G170" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Marlborough Place (IRE)</t>
+          <t>Dagger Strike (IRE)</t>
         </is>
       </c>
       <c r="I170" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J170" t="n">
-        <v>141</v>
+        <v>122</v>
       </c>
       <c r="K170" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="L170" t="n">
-        <v>17.1</v>
+        <v>19.35</v>
       </c>
       <c r="M170" t="n">
         <v>95.12</v>
       </c>
       <c r="N170" t="n">
-        <v>36.4</v>
+        <v>20.4</v>
       </c>
       <c r="O170" t="inlineStr">
         <is>
@@ -10601,40 +10497,24 @@
       <c r="F171" t="n">
         <v>4</v>
       </c>
-      <c r="G171" t="n">
-        <v>6</v>
-      </c>
+      <c r="G171" t="inlineStr"/>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Dagger Strike (IRE)</t>
-        </is>
-      </c>
-      <c r="I171" t="n">
-        <v>3</v>
-      </c>
-      <c r="J171" t="n">
-        <v>129</v>
-      </c>
-      <c r="K171" t="n">
-        <v>80</v>
-      </c>
-      <c r="L171" t="n">
-        <v>19.35</v>
-      </c>
-      <c r="M171" t="n">
-        <v>95.12</v>
-      </c>
-      <c r="N171" t="n">
-        <v>28.3</v>
-      </c>
+          <t>Huscal (IRE)</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr"/>
+      <c r="J171" t="inlineStr"/>
+      <c r="K171" t="inlineStr"/>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" t="inlineStr"/>
+      <c r="N171" t="inlineStr"/>
       <c r="O171" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P171" t="n">
-        <v>0</v>
-      </c>
+      <c r="P171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -10662,18 +10542,18 @@
         <v>6</v>
       </c>
       <c r="G172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Pay Attention</t>
+          <t>Quick Turn (FR)</t>
         </is>
       </c>
       <c r="I172" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J172" t="n">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="K172" t="n">
         <v>60</v>
@@ -10682,14 +10562,16 @@
       <c r="M172" t="n">
         <v>107.52</v>
       </c>
-      <c r="N172" t="inlineStr"/>
+      <c r="N172" t="n">
+        <v>42.6</v>
+      </c>
       <c r="O172" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P172" t="n">
-        <v>-7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="173">
@@ -10718,34 +10600,38 @@
         <v>6</v>
       </c>
       <c r="G173" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>U S S Constitution (IRE)</t>
+          <t>Rosemarys Rose (IRE)</t>
         </is>
       </c>
       <c r="I173" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J173" t="n">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="K173" t="n">
-        <v>59</v>
-      </c>
-      <c r="L173" t="inlineStr"/>
+        <v>57</v>
+      </c>
+      <c r="L173" t="n">
+        <v>1</v>
+      </c>
       <c r="M173" t="n">
         <v>107.52</v>
       </c>
-      <c r="N173" t="inlineStr"/>
+      <c r="N173" t="n">
+        <v>46.4</v>
+      </c>
       <c r="O173" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P173" t="n">
-        <v>-7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="174">
@@ -10774,34 +10660,38 @@
         <v>6</v>
       </c>
       <c r="G174" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Devious Devan (IRE)</t>
+          <t>Bobby Dassler (IRE)</t>
         </is>
       </c>
       <c r="I174" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J174" t="n">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="K174" t="n">
-        <v>58</v>
-      </c>
-      <c r="L174" t="inlineStr"/>
+        <v>56</v>
+      </c>
+      <c r="L174" t="n">
+        <v>12</v>
+      </c>
       <c r="M174" t="n">
         <v>107.52</v>
       </c>
-      <c r="N174" t="inlineStr"/>
+      <c r="N174" t="n">
+        <v>14.3</v>
+      </c>
       <c r="O174" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P174" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175">
@@ -10830,28 +10720,30 @@
         <v>6</v>
       </c>
       <c r="G175" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Quick Turn (FR)</t>
+          <t>Alices Influence</t>
         </is>
       </c>
       <c r="I175" t="n">
         <v>3</v>
       </c>
       <c r="J175" t="n">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="K175" t="n">
-        <v>60</v>
-      </c>
-      <c r="L175" t="inlineStr"/>
+        <v>53</v>
+      </c>
+      <c r="L175" t="n">
+        <v>13.25</v>
+      </c>
       <c r="M175" t="n">
         <v>107.52</v>
       </c>
       <c r="N175" t="n">
-        <v>50</v>
+        <v>11.1</v>
       </c>
       <c r="O175" t="inlineStr">
         <is>
@@ -10888,30 +10780,30 @@
         <v>6</v>
       </c>
       <c r="G176" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Rosemarys Rose (IRE)</t>
+          <t>Fifty Sent</t>
         </is>
       </c>
       <c r="I176" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J176" t="n">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="K176" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="L176" t="n">
-        <v>1</v>
+        <v>17.75</v>
       </c>
       <c r="M176" t="n">
         <v>107.52</v>
       </c>
       <c r="N176" t="n">
-        <v>46.4</v>
+        <v>-11.5</v>
       </c>
       <c r="O176" t="inlineStr">
         <is>
@@ -10947,40 +10839,24 @@
       <c r="F177" t="n">
         <v>6</v>
       </c>
-      <c r="G177" t="n">
-        <v>3</v>
-      </c>
+      <c r="G177" t="inlineStr"/>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Bobby Dassler (IRE)</t>
-        </is>
-      </c>
-      <c r="I177" t="n">
-        <v>7</v>
-      </c>
-      <c r="J177" t="n">
-        <v>138</v>
-      </c>
-      <c r="K177" t="n">
-        <v>56</v>
-      </c>
-      <c r="L177" t="n">
-        <v>12</v>
-      </c>
-      <c r="M177" t="n">
-        <v>107.52</v>
-      </c>
-      <c r="N177" t="n">
-        <v>16.4</v>
-      </c>
+          <t>U S S Constitution (IRE)</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr"/>
+      <c r="J177" t="inlineStr"/>
+      <c r="K177" t="inlineStr"/>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" t="inlineStr"/>
+      <c r="N177" t="inlineStr"/>
       <c r="O177" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P177" t="n">
-        <v>0</v>
-      </c>
+      <c r="P177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -11007,40 +10883,24 @@
       <c r="F178" t="n">
         <v>6</v>
       </c>
-      <c r="G178" t="n">
-        <v>4</v>
-      </c>
+      <c r="G178" t="inlineStr"/>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Alices Influence</t>
-        </is>
-      </c>
-      <c r="I178" t="n">
-        <v>3</v>
-      </c>
-      <c r="J178" t="n">
-        <v>125</v>
-      </c>
-      <c r="K178" t="n">
-        <v>53</v>
-      </c>
-      <c r="L178" t="n">
-        <v>13.25</v>
-      </c>
-      <c r="M178" t="n">
-        <v>107.52</v>
-      </c>
-      <c r="N178" t="n">
-        <v>11.1</v>
-      </c>
+          <t>Pay Attention</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr"/>
+      <c r="J178" t="inlineStr"/>
+      <c r="K178" t="inlineStr"/>
+      <c r="L178" t="inlineStr"/>
+      <c r="M178" t="inlineStr"/>
+      <c r="N178" t="inlineStr"/>
       <c r="O178" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P178" t="n">
-        <v>0</v>
-      </c>
+      <c r="P178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -11067,40 +10927,24 @@
       <c r="F179" t="n">
         <v>6</v>
       </c>
-      <c r="G179" t="n">
-        <v>5</v>
-      </c>
+      <c r="G179" t="inlineStr"/>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Fifty Sent</t>
-        </is>
-      </c>
-      <c r="I179" t="n">
-        <v>7</v>
-      </c>
-      <c r="J179" t="n">
-        <v>134</v>
-      </c>
-      <c r="K179" t="n">
-        <v>52</v>
-      </c>
-      <c r="L179" t="n">
-        <v>17.75</v>
-      </c>
-      <c r="M179" t="n">
-        <v>107.52</v>
-      </c>
-      <c r="N179" t="n">
-        <v>-2.7</v>
-      </c>
+          <t>Devious Devan (IRE)</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr"/>
+      <c r="J179" t="inlineStr"/>
+      <c r="K179" t="inlineStr"/>
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" t="inlineStr"/>
+      <c r="N179" t="inlineStr"/>
       <c r="O179" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P179" t="n">
-        <v>0</v>
-      </c>
+      <c r="P179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -11139,7 +10983,7 @@
         <v>3</v>
       </c>
       <c r="J180" t="n">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="K180" t="n">
         <v>0</v>
@@ -11149,7 +10993,7 @@
         <v>135.2</v>
       </c>
       <c r="N180" t="n">
-        <v>74.59999999999999</v>
+        <v>66</v>
       </c>
       <c r="O180" t="inlineStr">
         <is>
@@ -11377,7 +11221,7 @@
         <v>3</v>
       </c>
       <c r="J184" t="n">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="K184" t="n">
         <v>0</v>
@@ -11389,7 +11233,7 @@
         <v>135.2</v>
       </c>
       <c r="N184" t="n">
-        <v>49.5</v>
+        <v>45</v>
       </c>
       <c r="O184" t="inlineStr">
         <is>
@@ -11437,7 +11281,7 @@
         <v>3</v>
       </c>
       <c r="J185" t="n">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="K185" t="n">
         <v>0</v>
@@ -11449,7 +11293,7 @@
         <v>135.2</v>
       </c>
       <c r="N185" t="n">
-        <v>46</v>
+        <v>41.9</v>
       </c>
       <c r="O185" t="inlineStr">
         <is>
@@ -11606,11 +11450,11 @@
         <v>6</v>
       </c>
       <c r="G188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Tales Old As Time</t>
+          <t>Liveinthelight</t>
         </is>
       </c>
       <c r="I188" t="n">
@@ -11626,14 +11470,16 @@
       <c r="M188" t="n">
         <v>138.1</v>
       </c>
-      <c r="N188" t="inlineStr"/>
+      <c r="N188" t="n">
+        <v>52.4</v>
+      </c>
       <c r="O188" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P188" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="189">
@@ -11662,28 +11508,30 @@
         <v>6</v>
       </c>
       <c r="G189" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Liveinthelight</t>
+          <t>Grand Pier</t>
         </is>
       </c>
       <c r="I189" t="n">
         <v>3</v>
       </c>
       <c r="J189" t="n">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="K189" t="n">
-        <v>63</v>
-      </c>
-      <c r="L189" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="L189" t="n">
+        <v>0.5</v>
+      </c>
       <c r="M189" t="n">
         <v>138.1</v>
       </c>
       <c r="N189" t="n">
-        <v>52.4</v>
+        <v>41.2</v>
       </c>
       <c r="O189" t="inlineStr">
         <is>
@@ -11720,30 +11568,30 @@
         <v>6</v>
       </c>
       <c r="G190" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Grand Pier</t>
+          <t>Rajwaah</t>
         </is>
       </c>
       <c r="I190" t="n">
         <v>3</v>
       </c>
       <c r="J190" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="K190" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="L190" t="n">
-        <v>0.5</v>
+        <v>6.5</v>
       </c>
       <c r="M190" t="n">
         <v>138.1</v>
       </c>
       <c r="N190" t="n">
-        <v>48.3</v>
+        <v>37.2</v>
       </c>
       <c r="O190" t="inlineStr">
         <is>
@@ -11780,30 +11628,30 @@
         <v>6</v>
       </c>
       <c r="G191" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Rajwaah</t>
+          <t>Zooter</t>
         </is>
       </c>
       <c r="I191" t="n">
         <v>3</v>
       </c>
       <c r="J191" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="K191" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="L191" t="n">
-        <v>6.5</v>
+        <v>18.5</v>
       </c>
       <c r="M191" t="n">
         <v>138.1</v>
       </c>
       <c r="N191" t="n">
-        <v>37.2</v>
+        <v>14</v>
       </c>
       <c r="O191" t="inlineStr">
         <is>
@@ -11840,34 +11688,34 @@
         <v>6</v>
       </c>
       <c r="G192" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Zooter</t>
+          <t>Blue Jammin (IRE)</t>
         </is>
       </c>
       <c r="I192" t="n">
         <v>3</v>
       </c>
       <c r="J192" t="n">
-        <v>135</v>
+        <v>118</v>
       </c>
       <c r="K192" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="L192" t="n">
-        <v>18.5</v>
+        <v>24.5</v>
       </c>
       <c r="M192" t="n">
         <v>138.1</v>
       </c>
       <c r="N192" t="n">
-        <v>14</v>
+        <v>2.1</v>
       </c>
       <c r="O192" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="P192" t="n">
@@ -11899,40 +11747,24 @@
       <c r="F193" t="n">
         <v>6</v>
       </c>
-      <c r="G193" t="n">
-        <v>5</v>
-      </c>
+      <c r="G193" t="inlineStr"/>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Blue Jammin (IRE)</t>
-        </is>
-      </c>
-      <c r="I193" t="n">
-        <v>3</v>
-      </c>
-      <c r="J193" t="n">
-        <v>123</v>
-      </c>
-      <c r="K193" t="n">
-        <v>53</v>
-      </c>
-      <c r="L193" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="M193" t="n">
-        <v>138.1</v>
-      </c>
-      <c r="N193" t="n">
-        <v>12.7</v>
-      </c>
+          <t>Tales Old As Time</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr"/>
+      <c r="J193" t="inlineStr"/>
+      <c r="K193" t="inlineStr"/>
+      <c r="L193" t="inlineStr"/>
+      <c r="M193" t="inlineStr"/>
+      <c r="N193" t="inlineStr"/>
       <c r="O193" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="P193" t="n">
-        <v>0</v>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -12209,7 +12041,7 @@
         <v>6</v>
       </c>
       <c r="J198" t="n">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="K198" t="n">
         <v>56</v>
@@ -12221,7 +12053,7 @@
         <v>118.04</v>
       </c>
       <c r="N198" t="n">
-        <v>48.7</v>
+        <v>47.2</v>
       </c>
       <c r="O198" t="inlineStr">
         <is>
@@ -12269,7 +12101,7 @@
         <v>4</v>
       </c>
       <c r="J199" t="n">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="K199" t="n">
         <v>52</v>
@@ -12281,7 +12113,7 @@
         <v>118.04</v>
       </c>
       <c r="N199" t="n">
-        <v>42</v>
+        <v>38.2</v>
       </c>
       <c r="O199" t="inlineStr">
         <is>
@@ -12676,34 +12508,36 @@
         <v>4</v>
       </c>
       <c r="G206" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Tiva (IRE)</t>
+          <t>Solar Aclaim (IRE)</t>
         </is>
       </c>
       <c r="I206" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J206" t="n">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="K206" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="L206" t="inlineStr"/>
       <c r="M206" t="n">
         <v>57.62</v>
       </c>
-      <c r="N206" t="inlineStr"/>
+      <c r="N206" t="n">
+        <v>93.2</v>
+      </c>
       <c r="O206" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P206" t="n">
-        <v>-9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="207">
@@ -12732,28 +12566,30 @@
         <v>4</v>
       </c>
       <c r="G207" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Solar Aclaim (IRE)</t>
+          <t>Top Juggler (IRE)</t>
         </is>
       </c>
       <c r="I207" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J207" t="n">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="K207" t="n">
-        <v>84</v>
-      </c>
-      <c r="L207" t="inlineStr"/>
+        <v>78</v>
+      </c>
+      <c r="L207" t="n">
+        <v>2.25</v>
+      </c>
       <c r="M207" t="n">
         <v>57.62</v>
       </c>
       <c r="N207" t="n">
-        <v>93.2</v>
+        <v>87.2</v>
       </c>
       <c r="O207" t="inlineStr">
         <is>
@@ -12790,30 +12626,30 @@
         <v>4</v>
       </c>
       <c r="G208" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Top Juggler (IRE)</t>
+          <t>Montezuma</t>
         </is>
       </c>
       <c r="I208" t="n">
         <v>4</v>
       </c>
       <c r="J208" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="K208" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L208" t="n">
-        <v>2.25</v>
+        <v>4</v>
       </c>
       <c r="M208" t="n">
         <v>57.62</v>
       </c>
       <c r="N208" t="n">
-        <v>87.2</v>
+        <v>81.5</v>
       </c>
       <c r="O208" t="inlineStr">
         <is>
@@ -12821,7 +12657,7 @@
         </is>
       </c>
       <c r="P208" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="209">
@@ -12850,30 +12686,30 @@
         <v>4</v>
       </c>
       <c r="G209" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Montezuma</t>
+          <t>Jordan Electrics</t>
         </is>
       </c>
       <c r="I209" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J209" t="n">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="K209" t="n">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="L209" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="M209" t="n">
         <v>57.62</v>
       </c>
       <c r="N209" t="n">
-        <v>81.5</v>
+        <v>82</v>
       </c>
       <c r="O209" t="inlineStr">
         <is>
@@ -12881,7 +12717,7 @@
         </is>
       </c>
       <c r="P209" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="210">
@@ -12910,30 +12746,30 @@
         <v>4</v>
       </c>
       <c r="G210" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Jordan Electrics</t>
+          <t>Canaria Queen</t>
         </is>
       </c>
       <c r="I210" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J210" t="n">
-        <v>143</v>
+        <v>124</v>
       </c>
       <c r="K210" t="n">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="L210" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="M210" t="n">
         <v>57.62</v>
       </c>
       <c r="N210" t="n">
-        <v>82</v>
+        <v>63.6</v>
       </c>
       <c r="O210" t="inlineStr">
         <is>
@@ -12941,7 +12777,7 @@
         </is>
       </c>
       <c r="P210" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="211">
@@ -12970,30 +12806,30 @@
         <v>4</v>
       </c>
       <c r="G211" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Canaria Queen</t>
+          <t>Call Margot (IRE)</t>
         </is>
       </c>
       <c r="I211" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J211" t="n">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="K211" t="n">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="L211" t="n">
-        <v>6</v>
+        <v>9.25</v>
       </c>
       <c r="M211" t="n">
         <v>57.62</v>
       </c>
       <c r="N211" t="n">
-        <v>63.6</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="O211" t="inlineStr">
         <is>
@@ -13001,7 +12837,7 @@
         </is>
       </c>
       <c r="P211" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="212">
@@ -13030,30 +12866,30 @@
         <v>4</v>
       </c>
       <c r="G212" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Call Margot (IRE)</t>
+          <t>Jm Jhingree (IRE)</t>
         </is>
       </c>
       <c r="I212" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J212" t="n">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="K212" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="L212" t="n">
-        <v>9.25</v>
+        <v>11.5</v>
       </c>
       <c r="M212" t="n">
         <v>57.62</v>
       </c>
       <c r="N212" t="n">
-        <v>64.40000000000001</v>
+        <v>42.6</v>
       </c>
       <c r="O212" t="inlineStr">
         <is>
@@ -13061,7 +12897,7 @@
         </is>
       </c>
       <c r="P212" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="213">
@@ -13090,30 +12926,30 @@
         <v>4</v>
       </c>
       <c r="G213" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Jm Jhingree (IRE)</t>
+          <t>Classy Al</t>
         </is>
       </c>
       <c r="I213" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J213" t="n">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="K213" t="n">
         <v>66</v>
       </c>
       <c r="L213" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="M213" t="n">
         <v>57.62</v>
       </c>
       <c r="N213" t="n">
-        <v>42.6</v>
+        <v>33.4</v>
       </c>
       <c r="O213" t="inlineStr">
         <is>
@@ -13149,40 +12985,24 @@
       <c r="F214" t="n">
         <v>4</v>
       </c>
-      <c r="G214" t="n">
-        <v>8</v>
-      </c>
+      <c r="G214" t="inlineStr"/>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Classy Al</t>
-        </is>
-      </c>
-      <c r="I214" t="n">
-        <v>8</v>
-      </c>
-      <c r="J214" t="n">
-        <v>123</v>
-      </c>
-      <c r="K214" t="n">
-        <v>66</v>
-      </c>
-      <c r="L214" t="n">
-        <v>14</v>
-      </c>
-      <c r="M214" t="n">
-        <v>57.62</v>
-      </c>
-      <c r="N214" t="n">
-        <v>35.2</v>
-      </c>
+          <t>Tiva (IRE)</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr"/>
+      <c r="J214" t="inlineStr"/>
+      <c r="K214" t="inlineStr"/>
+      <c r="L214" t="inlineStr"/>
+      <c r="M214" t="inlineStr"/>
+      <c r="N214" t="inlineStr"/>
       <c r="O214" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P214" t="n">
-        <v>0</v>
-      </c>
+      <c r="P214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -13539,7 +13359,7 @@
         </is>
       </c>
       <c r="P220" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="221">
@@ -13579,7 +13399,7 @@
         <v>4</v>
       </c>
       <c r="J221" t="n">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="K221" t="n">
         <v>69</v>
@@ -13591,7 +13411,7 @@
         <v>70.58</v>
       </c>
       <c r="N221" t="n">
-        <v>60.2</v>
+        <v>55.8</v>
       </c>
       <c r="O221" t="inlineStr">
         <is>
@@ -13599,7 +13419,7 @@
         </is>
       </c>
       <c r="P221" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="222">
@@ -13639,7 +13459,7 @@
         <v>6</v>
       </c>
       <c r="J222" t="n">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="K222" t="n">
         <v>51</v>
@@ -13651,7 +13471,7 @@
         <v>70.58</v>
       </c>
       <c r="N222" t="n">
-        <v>39.8</v>
+        <v>38.5</v>
       </c>
       <c r="O222" t="inlineStr">
         <is>
@@ -13688,34 +13508,36 @@
         <v>5</v>
       </c>
       <c r="G223" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Hot And Cold</t>
+          <t>Bearin Up (IRE)</t>
         </is>
       </c>
       <c r="I223" t="n">
         <v>3</v>
       </c>
       <c r="J223" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="K223" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="L223" t="inlineStr"/>
       <c r="M223" t="n">
         <v>106.82</v>
       </c>
-      <c r="N223" t="inlineStr"/>
+      <c r="N223" t="n">
+        <v>61.3</v>
+      </c>
       <c r="O223" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P223" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="224">
@@ -13744,28 +13566,30 @@
         <v>5</v>
       </c>
       <c r="G224" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Bearin Up (IRE)</t>
+          <t>Geo (IRE)</t>
         </is>
       </c>
       <c r="I224" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J224" t="n">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="K224" t="n">
-        <v>73</v>
-      </c>
-      <c r="L224" t="inlineStr"/>
+        <v>67</v>
+      </c>
+      <c r="L224" t="n">
+        <v>0.15</v>
+      </c>
       <c r="M224" t="n">
         <v>106.82</v>
       </c>
       <c r="N224" t="n">
-        <v>61.3</v>
+        <v>59.6</v>
       </c>
       <c r="O224" t="inlineStr">
         <is>
@@ -13802,30 +13626,30 @@
         <v>5</v>
       </c>
       <c r="G225" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Geo (IRE)</t>
+          <t>Porth Eilian</t>
         </is>
       </c>
       <c r="I225" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J225" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="K225" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="L225" t="n">
-        <v>0.15</v>
+        <v>3.4</v>
       </c>
       <c r="M225" t="n">
         <v>106.82</v>
       </c>
       <c r="N225" t="n">
-        <v>59.6</v>
+        <v>57</v>
       </c>
       <c r="O225" t="inlineStr">
         <is>
@@ -13862,30 +13686,30 @@
         <v>5</v>
       </c>
       <c r="G226" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Porth Eilian</t>
+          <t>Second Fiddle (IRE)</t>
         </is>
       </c>
       <c r="I226" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J226" t="n">
         <v>132</v>
       </c>
       <c r="K226" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="L226" t="n">
-        <v>3.4</v>
+        <v>7.9</v>
       </c>
       <c r="M226" t="n">
         <v>106.82</v>
       </c>
       <c r="N226" t="n">
-        <v>57</v>
+        <v>42.5</v>
       </c>
       <c r="O226" t="inlineStr">
         <is>
@@ -13922,30 +13746,30 @@
         <v>5</v>
       </c>
       <c r="G227" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Second Fiddle (IRE)</t>
+          <t>Epidavros (IRE)</t>
         </is>
       </c>
       <c r="I227" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J227" t="n">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="K227" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="L227" t="n">
-        <v>7.9</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="M227" t="n">
         <v>106.82</v>
       </c>
       <c r="N227" t="n">
-        <v>42.5</v>
+        <v>39</v>
       </c>
       <c r="O227" t="inlineStr">
         <is>
@@ -13953,7 +13777,7 @@
         </is>
       </c>
       <c r="P227" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="228">
@@ -13982,38 +13806,38 @@
         <v>5</v>
       </c>
       <c r="G228" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Epidavros (IRE)</t>
+          <t>Sound Janet</t>
         </is>
       </c>
       <c r="I228" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J228" t="n">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="K228" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="L228" t="n">
-        <v>8.050000000000001</v>
+        <v>20.05</v>
       </c>
       <c r="M228" t="n">
         <v>106.82</v>
       </c>
       <c r="N228" t="n">
-        <v>46.9</v>
+        <v>30.1</v>
       </c>
       <c r="O228" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="P228" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="229">
@@ -14041,40 +13865,24 @@
       <c r="F229" t="n">
         <v>5</v>
       </c>
-      <c r="G229" t="n">
-        <v>6</v>
-      </c>
+      <c r="G229" t="inlineStr"/>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Sound Janet</t>
-        </is>
-      </c>
-      <c r="I229" t="n">
-        <v>4</v>
-      </c>
-      <c r="J229" t="n">
-        <v>139</v>
-      </c>
-      <c r="K229" t="n">
-        <v>72</v>
-      </c>
-      <c r="L229" t="n">
-        <v>20.05</v>
-      </c>
-      <c r="M229" t="n">
-        <v>106.82</v>
-      </c>
-      <c r="N229" t="n">
-        <v>30.1</v>
-      </c>
+          <t>Hot And Cold</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr"/>
+      <c r="J229" t="inlineStr"/>
+      <c r="K229" t="inlineStr"/>
+      <c r="L229" t="inlineStr"/>
+      <c r="M229" t="inlineStr"/>
+      <c r="N229" t="inlineStr"/>
       <c r="O229" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="P229" t="n">
-        <v>0</v>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -14411,7 +14219,7 @@
         <v>3</v>
       </c>
       <c r="J235" t="n">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="K235" t="n">
         <v>57</v>
@@ -14423,7 +14231,7 @@
         <v>104.79</v>
       </c>
       <c r="N235" t="n">
-        <v>41.1</v>
+        <v>37.2</v>
       </c>
       <c r="O235" t="inlineStr">
         <is>
@@ -14709,7 +14517,7 @@
         <v>4</v>
       </c>
       <c r="J240" t="n">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="K240" t="n">
         <v>53</v>
@@ -14721,7 +14529,7 @@
         <v>142.87</v>
       </c>
       <c r="N240" t="n">
-        <v>49.5</v>
+        <v>45.2</v>
       </c>
       <c r="O240" t="inlineStr">
         <is>
@@ -15843,7 +15651,7 @@
         <v>7</v>
       </c>
       <c r="J259" t="n">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="K259" t="n">
         <v>76</v>
@@ -15855,7 +15663,7 @@
         <v>153.84</v>
       </c>
       <c r="N259" t="n">
-        <v>55.4</v>
+        <v>50.4</v>
       </c>
       <c r="O259" t="inlineStr">
         <is>
@@ -16261,7 +16069,7 @@
         <v>8</v>
       </c>
       <c r="J266" t="n">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="K266" t="n">
         <v>73</v>
@@ -16273,7 +16081,7 @@
         <v>70.75</v>
       </c>
       <c r="N266" t="n">
-        <v>56.5</v>
+        <v>52</v>
       </c>
       <c r="O266" t="inlineStr">
         <is>
@@ -16519,7 +16327,7 @@
         </is>
       </c>
       <c r="P270" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="271">
@@ -16579,7 +16387,7 @@
         </is>
       </c>
       <c r="P271" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="272">
@@ -16619,7 +16427,7 @@
         <v>5</v>
       </c>
       <c r="J272" t="n">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="K272" t="n">
         <v>70</v>
@@ -16631,7 +16439,7 @@
         <v>122.86</v>
       </c>
       <c r="N272" t="n">
-        <v>55.9</v>
+        <v>53.8</v>
       </c>
       <c r="O272" t="inlineStr">
         <is>
@@ -16639,7 +16447,7 @@
         </is>
       </c>
       <c r="P272" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="273">
@@ -16788,34 +16596,36 @@
         <v>6</v>
       </c>
       <c r="G275" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>You Mystify Me (IRE)</t>
+          <t>What A Tahoo (IRE)</t>
         </is>
       </c>
       <c r="I275" t="n">
         <v>3</v>
       </c>
       <c r="J275" t="n">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="K275" t="n">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="n">
         <v>58.64</v>
       </c>
-      <c r="N275" t="inlineStr"/>
+      <c r="N275" t="n">
+        <v>60.6</v>
+      </c>
       <c r="O275" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P275" t="n">
-        <v>-9</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="276">
@@ -16844,28 +16654,30 @@
         <v>6</v>
       </c>
       <c r="G276" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>What A Tahoo (IRE)</t>
+          <t>Barmyblade (IRE)</t>
         </is>
       </c>
       <c r="I276" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J276" t="n">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="K276" t="n">
-        <v>46</v>
-      </c>
-      <c r="L276" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="L276" t="n">
+        <v>1</v>
+      </c>
       <c r="M276" t="n">
         <v>58.64</v>
       </c>
       <c r="N276" t="n">
-        <v>60.6</v>
+        <v>61.1</v>
       </c>
       <c r="O276" t="inlineStr">
         <is>
@@ -16873,7 +16685,7 @@
         </is>
       </c>
       <c r="P276" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="277">
@@ -16902,30 +16714,30 @@
         <v>6</v>
       </c>
       <c r="G277" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>Barmyblade (IRE)</t>
+          <t>Brain Freeze (IRE)</t>
         </is>
       </c>
       <c r="I277" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J277" t="n">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="K277" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="L277" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="M277" t="n">
         <v>58.64</v>
       </c>
       <c r="N277" t="n">
-        <v>61.1</v>
+        <v>54.3</v>
       </c>
       <c r="O277" t="inlineStr">
         <is>
@@ -16933,7 +16745,7 @@
         </is>
       </c>
       <c r="P277" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="278">
@@ -16962,30 +16774,30 @@
         <v>6</v>
       </c>
       <c r="G278" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>Brain Freeze (IRE)</t>
+          <t>Doralee</t>
         </is>
       </c>
       <c r="I278" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J278" t="n">
         <v>133</v>
       </c>
       <c r="K278" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="L278" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="M278" t="n">
         <v>58.64</v>
       </c>
       <c r="N278" t="n">
-        <v>58.4</v>
+        <v>47.9</v>
       </c>
       <c r="O278" t="inlineStr">
         <is>
@@ -17022,30 +16834,30 @@
         <v>6</v>
       </c>
       <c r="G279" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>Doralee</t>
+          <t>Tanaka (IRE)</t>
         </is>
       </c>
       <c r="I279" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J279" t="n">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="K279" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="L279" t="n">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="M279" t="n">
         <v>58.64</v>
       </c>
       <c r="N279" t="n">
-        <v>47.9</v>
+        <v>42.1</v>
       </c>
       <c r="O279" t="inlineStr">
         <is>
@@ -17082,30 +16894,30 @@
         <v>6</v>
       </c>
       <c r="G280" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>Tanaka (IRE)</t>
+          <t>Arlington</t>
         </is>
       </c>
       <c r="I280" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J280" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="K280" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L280" t="n">
-        <v>4.55</v>
+        <v>5.3</v>
       </c>
       <c r="M280" t="n">
         <v>58.64</v>
       </c>
       <c r="N280" t="n">
-        <v>42.1</v>
+        <v>35.2</v>
       </c>
       <c r="O280" t="inlineStr">
         <is>
@@ -17113,7 +16925,7 @@
         </is>
       </c>
       <c r="P280" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="281">
@@ -17142,30 +16954,30 @@
         <v>6</v>
       </c>
       <c r="G281" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>Arlington</t>
+          <t>Dunnington Lad (IRE)</t>
         </is>
       </c>
       <c r="I281" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J281" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="K281" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L281" t="n">
-        <v>5.3</v>
+        <v>6.3</v>
       </c>
       <c r="M281" t="n">
         <v>58.64</v>
       </c>
       <c r="N281" t="n">
-        <v>39.9</v>
+        <v>35.7</v>
       </c>
       <c r="O281" t="inlineStr">
         <is>
@@ -17173,7 +16985,7 @@
         </is>
       </c>
       <c r="P281" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="282">
@@ -17202,15 +17014,15 @@
         <v>6</v>
       </c>
       <c r="G282" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>Dunnington Lad (IRE)</t>
+          <t>Hyrcanian (IRE)</t>
         </is>
       </c>
       <c r="I282" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J282" t="n">
         <v>130</v>
@@ -17219,13 +17031,13 @@
         <v>45</v>
       </c>
       <c r="L282" t="n">
-        <v>6.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M282" t="n">
         <v>58.64</v>
       </c>
       <c r="N282" t="n">
-        <v>35.7</v>
+        <v>30.8</v>
       </c>
       <c r="O282" t="inlineStr">
         <is>
@@ -17261,40 +17073,24 @@
       <c r="F283" t="n">
         <v>6</v>
       </c>
-      <c r="G283" t="n">
-        <v>8</v>
-      </c>
+      <c r="G283" t="inlineStr"/>
       <c r="H283" t="inlineStr">
         <is>
-          <t>Hyrcanian (IRE)</t>
-        </is>
-      </c>
-      <c r="I283" t="n">
-        <v>5</v>
-      </c>
-      <c r="J283" t="n">
-        <v>130</v>
-      </c>
-      <c r="K283" t="n">
-        <v>45</v>
-      </c>
-      <c r="L283" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="M283" t="n">
-        <v>58.64</v>
-      </c>
-      <c r="N283" t="n">
-        <v>30.8</v>
-      </c>
+          <t>You Mystify Me (IRE)</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr"/>
+      <c r="J283" t="inlineStr"/>
+      <c r="K283" t="inlineStr"/>
+      <c r="L283" t="inlineStr"/>
+      <c r="M283" t="inlineStr"/>
+      <c r="N283" t="inlineStr"/>
       <c r="O283" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P283" t="n">
-        <v>0</v>
-      </c>
+      <c r="P283" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
